--- a/Data/FlightPlan/FPL_16SEP26.xlsx
+++ b/Data/FlightPlan/FPL_16SEP26.xlsx
@@ -167,927 +167,963 @@
     <t>20:50</t>
   </si>
   <si>
+    <t>22:16</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>VN-A202</t>
+  </si>
+  <si>
+    <t>SGN</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>13:44</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>23:03</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>VN-A203</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>13:51</t>
+  </si>
+  <si>
+    <t>PQC</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>16:01</t>
+  </si>
+  <si>
+    <t>ICN</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>01:18</t>
+  </si>
+  <si>
+    <t>VN-A500</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:19</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>11:56</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>14:36</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>18:03</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>23:42</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>VN-A521</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>15:08</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A523</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>18:12</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>19:32</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>VN-A524</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>14:41</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>18:11</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>23:39</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>10:03</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>13:26</t>
+  </si>
+  <si>
+    <t>17:54</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>20:28</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>10:14</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>17:34</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>11:58</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>19:26</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>22:23</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>06:34</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>17:19</t>
+  </si>
+  <si>
+    <t>20:18</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>10:16</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>13:02</t>
+  </si>
+  <si>
+    <t>15:26</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>11:12</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>14:48</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>17:17</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>19:53</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>21:34</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>23:22</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:16</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>09:08</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>11:02</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>12:48</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>22:24</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>11:53</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>15:23</t>
+  </si>
+  <si>
+    <t>18:17</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>20:59</t>
+  </si>
+  <si>
+    <t>22:51</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>08:59</t>
+  </si>
+  <si>
+    <t>11:36</t>
+  </si>
+  <si>
+    <t>20:13</t>
+  </si>
+  <si>
+    <t>00:49</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:02</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>20:21</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>16:57</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>20:01</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>23:16</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>13:19</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>23:40</t>
+  </si>
+  <si>
+    <t>00:26</t>
+  </si>
+  <si>
+    <t>00:40</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>17:53</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>13:06</t>
+  </si>
+  <si>
+    <t>22:03</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>19:13</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>23:02</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>5069 *</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>09:43</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>15:31</t>
+  </si>
+  <si>
+    <t>BAX</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>00:22</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>07:11</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>10:56</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>08:02</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>16:31</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>19:58</t>
+  </si>
+  <si>
+    <t>22:21</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>14:42</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>21:59</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>06:44</t>
+  </si>
+  <si>
+    <t>08:44</t>
+  </si>
+  <si>
+    <t>10:59</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>13:04</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>18:29</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>15:21</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>16:53</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>17:01</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>19:03</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>20:34</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>22:26</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>11:54</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>18:42</t>
+  </si>
+  <si>
+    <t>20:57</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>22:52</t>
+  </si>
+  <si>
     <t>22:05</t>
   </si>
   <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>VN-A202</t>
-  </si>
-  <si>
-    <t>SGN</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>13:44</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>23:03</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>VN-A203</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>13:51</t>
-  </si>
-  <si>
-    <t>PQC</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>16:01</t>
-  </si>
-  <si>
-    <t>ICN</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>01:18</t>
-  </si>
-  <si>
-    <t>VN-A500</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:19</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>11:56</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>14:36</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>18:03</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>23:42</t>
-  </si>
-  <si>
-    <t>23:50</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>VN-A521</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>15:08</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A523</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>18:12</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>19:32</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>VN-A524</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>14:41</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>18:11</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>23:39</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>10:03</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>13:26</t>
-  </si>
-  <si>
-    <t>17:54</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>20:28</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>10:14</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>17:34</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>11:58</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>19:26</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>22:19</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>06:34</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>17:19</t>
-  </si>
-  <si>
-    <t>20:18</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>10:16</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>13:02</t>
-  </si>
-  <si>
-    <t>15:26</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>11:12</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>14:48</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>17:17</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>19:53</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>23:40</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:16</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>09:08</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>11:02</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>12:48</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>22:08</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>11:53</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>15:23</t>
-  </si>
-  <si>
-    <t>18:17</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>20:59</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>08:59</t>
-  </si>
-  <si>
-    <t>11:36</t>
-  </si>
-  <si>
-    <t>20:13</t>
-  </si>
-  <si>
-    <t>00:49</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:02</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>20:21</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>16:57</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>20:01</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>13:19</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>00:14</t>
-  </si>
-  <si>
-    <t>00:40</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>17:53</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>13:06</t>
-  </si>
-  <si>
-    <t>22:03</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>19:13</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>5069 *</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>09:43</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>15:31</t>
-  </si>
-  <si>
-    <t>BAX</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>00:22</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>07:11</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>10:56</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>08:02</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>16:31</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>19:58</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>14:42</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>06:44</t>
-  </si>
-  <si>
-    <t>08:44</t>
-  </si>
-  <si>
-    <t>10:59</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>13:04</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>18:29</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>15:21</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>16:53</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>17:01</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>19:03</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>20:34</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>11:54</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>18:42</t>
-  </si>
-  <si>
-    <t>20:57</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
     <t>VN-A641</t>
   </si>
   <si>
@@ -1193,6 +1229,9 @@
     <t>01:30</t>
   </si>
   <si>
+    <t>01:52</t>
+  </si>
+  <si>
     <t>02:30</t>
   </si>
   <si>
@@ -1241,6 +1280,9 @@
     <t>20:31</t>
   </si>
   <si>
+    <t>22:44</t>
+  </si>
+  <si>
     <t>VN-A647</t>
   </si>
   <si>
@@ -1268,6 +1310,9 @@
     <t>21:16</t>
   </si>
   <si>
+    <t>23:34</t>
+  </si>
+  <si>
     <t>VN-A648</t>
   </si>
   <si>
@@ -1424,7 +1469,7 @@
     <t>13:40</t>
   </si>
   <si>
-    <t>21:14</t>
+    <t>21:23</t>
   </si>
   <si>
     <t>VN-A658</t>
@@ -1439,6 +1484,9 @@
     <t>16:29</t>
   </si>
   <si>
+    <t>23:09</t>
+  </si>
+  <si>
     <t>771A *</t>
   </si>
   <si>
@@ -1487,7 +1535,7 @@
     <t>21:50</t>
   </si>
   <si>
-    <t>22:34</t>
+    <t>22:33</t>
   </si>
   <si>
     <t>VN-A669</t>
@@ -1526,6 +1574,9 @@
     <t>20:46</t>
   </si>
   <si>
+    <t>22:42</t>
+  </si>
+  <si>
     <t>VN-A671</t>
   </si>
   <si>
@@ -1577,7 +1628,7 @@
     <t>PVG</t>
   </si>
   <si>
-    <t>01:14</t>
+    <t>01:45</t>
   </si>
   <si>
     <t>02:15</t>
@@ -1613,7 +1664,7 @@
     <t>19:56</t>
   </si>
   <si>
-    <t>01:15</t>
+    <t>01:19</t>
   </si>
   <si>
     <t>02:20</t>
@@ -1640,6 +1691,9 @@
     <t>20:47</t>
   </si>
   <si>
+    <t>23:43</t>
+  </si>
+  <si>
     <t>VN-A683</t>
   </si>
   <si>
@@ -1667,9 +1721,6 @@
     <t>12:34</t>
   </si>
   <si>
-    <t>21:34</t>
-  </si>
-  <si>
     <t>MNL</t>
   </si>
   <si>
@@ -1700,7 +1751,7 @@
     <t>19:49</t>
   </si>
   <si>
-    <t>22:02</t>
+    <t>21:57</t>
   </si>
   <si>
     <t>FUK</t>
@@ -1724,6 +1775,9 @@
     <t>20:39</t>
   </si>
   <si>
+    <t>22:37</t>
+  </si>
+  <si>
     <t>VN-A689</t>
   </si>
   <si>
@@ -1736,9 +1790,6 @@
     <t>19:16</t>
   </si>
   <si>
-    <t>00:24</t>
-  </si>
-  <si>
     <t>01:20</t>
   </si>
   <si>
@@ -1769,6 +1820,9 @@
     <t>VN-A697</t>
   </si>
   <si>
+    <t>23:49</t>
+  </si>
+  <si>
     <t>VN-A698</t>
   </si>
   <si>
@@ -1835,6 +1889,9 @@
     <t>SYD</t>
   </si>
   <si>
+    <t>08:34</t>
+  </si>
+  <si>
     <t>VN-A815</t>
   </si>
   <si>
@@ -1868,7 +1925,7 @@
     <t>Total Record(s): 387</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 16, 2026 20:23</t>
+    <t xml:space="preserve">Generated on  Sep 16, 2026 22:18</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5655,7 +5712,9 @@
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
-      <c r="M108" s="7"/>
+      <c t="s" r="M108" s="7">
+        <v>242</v>
+      </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c t="s" r="A109" s="6">
@@ -5681,10 +5740,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5717,7 +5776,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5729,7 +5788,7 @@
         <v>195</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J111" s="7">
         <v>81</v>
@@ -5737,7 +5796,7 @@
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5752,7 +5811,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5772,7 +5831,7 @@
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5787,7 +5846,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5807,7 +5866,7 @@
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5822,7 +5881,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5842,7 +5901,7 @@
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c t="s" r="M114" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -5872,7 +5931,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5884,7 +5943,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>112</v>
@@ -5892,7 +5951,7 @@
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5907,7 +5966,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5927,7 +5986,7 @@
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5942,7 +6001,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5957,12 +6016,12 @@
         <v>128</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5992,7 +6051,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -6001,13 +6060,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -6027,13 +6086,13 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>57</v>
@@ -6047,7 +6106,7 @@
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -6062,7 +6121,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -6074,15 +6133,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -6097,7 +6156,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -6112,11 +6171,13 @@
         <v>173</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
-      <c r="M123" s="7"/>
+      <c t="s" r="M123" s="7">
+        <v>265</v>
+      </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c t="s" r="A124" s="6">
@@ -6130,7 +6191,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -6147,9 +6208,13 @@
       <c t="s" r="J124" s="7">
         <v>181</v>
       </c>
-      <c r="K124" s="7"/>
+      <c t="s" r="K124" s="7">
+        <v>266</v>
+      </c>
       <c r="L124" s="7"/>
-      <c r="M124" s="7"/>
+      <c t="s" r="M124" s="7">
+        <v>267</v>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c r="A125" s="6"/>
@@ -6178,7 +6243,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -6187,7 +6252,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I126" s="7">
         <v>193</v>
@@ -6198,7 +6263,7 @@
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -6213,22 +6278,22 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H127" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -6248,7 +6313,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -6257,18 +6322,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="I128" s="7">
         <v>103</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>217</v>
+        <v>273</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -6283,19 +6348,19 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>137</v>
@@ -6331,7 +6396,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6351,7 +6416,7 @@
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6366,7 +6431,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6378,7 +6443,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>115</v>
@@ -6388,7 +6453,7 @@
       </c>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -6403,7 +6468,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6436,7 +6501,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6445,13 +6510,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -6484,7 +6549,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6499,12 +6564,12 @@
         <v>69</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -6519,7 +6584,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6554,7 +6619,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6574,7 +6639,7 @@
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6604,7 +6669,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6619,7 +6684,7 @@
         <v>235</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -6639,7 +6704,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6648,10 +6713,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>77</v>
@@ -6674,19 +6739,19 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>24</v>
@@ -6694,7 +6759,7 @@
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6709,7 +6774,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6721,10 +6786,10 @@
         <v>179</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6744,7 +6809,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6756,14 +6821,16 @@
         <v>57</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
-      <c r="M144" s="7"/>
+      <c t="s" r="M144" s="7">
+        <v>295</v>
+      </c>
     </row>
     <row r="145" ht="15" customHeight="1">
       <c t="s" r="A145" s="6">
@@ -6777,7 +6844,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6825,7 +6892,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6840,12 +6907,12 @@
         <v>181</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6860,7 +6927,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6869,7 +6936,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="I148" s="7">
         <v>59</v>
@@ -6895,13 +6962,13 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>34</v>
@@ -6910,12 +6977,12 @@
         <v>91</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>214</v>
+        <v>300</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6930,7 +6997,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6942,10 +7009,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6971,14 +7038,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B152" s="7">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c t="s" r="C152" s="7">
         <v>146</v>
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6990,17 +7057,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>35</v>
       </c>
       <c t="s" r="K152" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -7015,7 +7082,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -7030,12 +7097,12 @@
         <v>155</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -7050,7 +7117,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -7059,10 +7126,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>64</v>
@@ -7085,19 +7152,19 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>184</v>
@@ -7133,7 +7200,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -7148,7 +7215,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -7168,7 +7235,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -7177,7 +7244,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c t="s" r="I158" s="7">
         <v>102</v>
@@ -7188,7 +7255,7 @@
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -7203,22 +7270,22 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -7251,7 +7318,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -7260,18 +7327,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>314</v>
+        <v>321</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -7286,19 +7353,19 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c t="s" r="J162" s="7">
         <v>184</v>
@@ -7338,7 +7405,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7353,12 +7420,12 @@
         <v>192</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7388,7 +7455,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7408,7 +7475,7 @@
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7423,7 +7490,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7438,7 +7505,7 @@
         <v>205</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -7458,7 +7525,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7470,7 +7537,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c t="s" r="J168" s="7">
         <v>102</v>
@@ -7478,7 +7545,7 @@
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7493,7 +7560,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7505,15 +7572,15 @@
         <v>107</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>324</v>
+        <v>331</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7528,7 +7595,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7547,7 +7614,9 @@
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
-      <c r="M170" s="7"/>
+      <c t="s" r="M170" s="7">
+        <v>332</v>
+      </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
       <c t="s" r="A171" s="6">
@@ -7561,7 +7630,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7573,7 +7642,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>78</v>
@@ -7609,7 +7678,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7621,7 +7690,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>109</v>
@@ -7644,7 +7713,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7656,15 +7725,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7679,7 +7748,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7691,14 +7760,16 @@
         <v>57</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>216</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
-      <c r="M175" s="7"/>
+      <c t="s" r="M175" s="7">
+        <v>339</v>
+      </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
       <c r="A176" s="6"/>
@@ -7727,7 +7798,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7747,7 +7818,7 @@
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>332</v>
+        <v>341</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7762,7 +7833,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7782,7 +7853,7 @@
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>333</v>
+        <v>342</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7797,7 +7868,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7817,7 +7888,7 @@
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7832,7 +7903,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7844,15 +7915,15 @@
         <v>44</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7867,7 +7938,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7879,7 +7950,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>198</v>
@@ -7902,7 +7973,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7917,12 +7988,12 @@
         <v>102</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>339</v>
+        <v>348</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7952,7 +8023,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7972,7 +8043,7 @@
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -7987,7 +8058,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -8002,10 +8073,10 @@
         <v>35</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c t="s" r="K185" s="7">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
@@ -8024,7 +8095,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -8039,14 +8110,14 @@
         <v>205</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="K186" s="7">
         <v>85</v>
       </c>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>336</v>
+        <v>345</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -8061,7 +8132,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -8070,10 +8141,10 @@
         <v>44</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>156</v>
@@ -8081,7 +8152,7 @@
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>342</v>
+        <v>351</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -8096,13 +8167,13 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>44</v>
@@ -8111,12 +8182,12 @@
         <v>74</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>344</v>
+        <v>353</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -8146,7 +8217,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -8155,13 +8226,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="I190" s="7">
         <v>100</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -8181,19 +8252,19 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J191" s="7">
         <v>157</v>
@@ -8201,7 +8272,7 @@
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8216,7 +8287,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -8225,7 +8296,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c t="s" r="I192" s="7">
         <v>210</v>
@@ -8236,7 +8307,7 @@
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>348</v>
+        <v>357</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8251,13 +8322,13 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>57</v>
@@ -8266,12 +8337,12 @@
         <v>46</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -8286,7 +8357,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8298,14 +8369,16 @@
         <v>44</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>175</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
-      <c r="M194" s="7"/>
+      <c t="s" r="M194" s="7">
+        <v>361</v>
+      </c>
     </row>
     <row r="195" ht="15" customHeight="1">
       <c t="s" r="A195" s="6">
@@ -8319,7 +8392,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8331,10 +8404,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -8367,7 +8440,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8379,7 +8452,7 @@
         <v>154</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>123</v>
@@ -8402,7 +8475,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8422,7 +8495,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8437,7 +8510,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8457,7 +8530,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8472,7 +8545,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8487,14 +8560,14 @@
         <v>227</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c t="s" r="K200" s="7">
         <v>61</v>
       </c>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8509,7 +8582,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8521,7 +8594,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="J201" s="7">
         <v>210</v>
@@ -8529,7 +8602,7 @@
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8544,7 +8617,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8566,7 +8639,7 @@
       </c>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8581,7 +8654,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8593,17 +8666,17 @@
         <v>44</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c t="s" r="K203" s="7">
         <v>201</v>
       </c>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>64</v>
+        <v>369</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8618,7 +8691,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8630,10 +8703,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>52</v>
+        <v>370</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="K204" s="7">
         <v>232</v>
@@ -8670,7 +8743,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8685,7 +8758,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8705,7 +8778,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8725,7 +8798,7 @@
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>361</v>
+        <v>373</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8740,7 +8813,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8752,7 +8825,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>19</v>
@@ -8760,7 +8833,7 @@
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>362</v>
+        <v>374</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8775,7 +8848,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8797,7 +8870,7 @@
       </c>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8812,7 +8885,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8827,14 +8900,14 @@
         <v>102</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c t="s" r="K210" s="7">
         <v>186</v>
       </c>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>365</v>
+        <v>377</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8849,7 +8922,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8861,17 +8934,17 @@
         <v>107</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c t="s" r="K211" s="7">
         <v>173</v>
       </c>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>131</v>
+        <v>27</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8886,7 +8959,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8898,17 +8971,17 @@
         <v>57</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c t="s" r="K212" s="7">
         <v>27</v>
       </c>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8938,7 +9011,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8958,7 +9031,7 @@
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8973,7 +9046,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8988,12 +9061,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>371</v>
+        <v>383</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -9008,7 +9081,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -9017,7 +9090,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c t="s" r="I216" s="7">
         <v>90</v>
@@ -9028,7 +9101,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>339</v>
+        <v>348</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -9043,13 +9116,13 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>57</v>
@@ -9058,7 +9131,7 @@
         <v>94</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -9093,7 +9166,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -9113,7 +9186,7 @@
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>374</v>
+        <v>386</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -9128,7 +9201,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -9140,15 +9213,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>377</v>
+        <v>389</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -9163,7 +9236,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -9172,10 +9245,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>74</v>
@@ -9183,7 +9256,7 @@
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>379</v>
+        <v>391</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -9198,27 +9271,27 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>382</v>
+        <v>394</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -9233,7 +9306,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9245,7 +9318,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>173</v>
@@ -9253,7 +9326,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>384</v>
+        <v>396</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -9268,7 +9341,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -9280,13 +9353,13 @@
         <v>57</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>66</v>
       </c>
       <c t="s" r="K224" s="7">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
@@ -9320,7 +9393,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9332,7 +9405,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>82</v>
@@ -9340,7 +9413,7 @@
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>387</v>
+        <v>399</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9355,7 +9428,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9370,12 +9443,12 @@
         <v>161</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>388</v>
+        <v>400</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -9390,7 +9463,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9405,14 +9478,14 @@
         <v>88</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="K228" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9427,7 +9500,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9439,10 +9512,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c t="s" r="K229" s="7">
         <v>91</v>
@@ -9464,7 +9537,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9476,17 +9549,17 @@
         <v>174</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c t="s" r="K230" s="7">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>309</v>
+        <v>406</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9501,7 +9574,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9513,17 +9586,17 @@
         <v>57</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c t="s" r="K231" s="7">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>397</v>
+        <v>410</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9553,7 +9626,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9565,7 +9638,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>81</v>
@@ -9573,7 +9646,7 @@
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>400</v>
+        <v>413</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9588,7 +9661,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9600,7 +9673,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>205</v>
@@ -9608,7 +9681,7 @@
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9623,7 +9696,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9643,7 +9716,7 @@
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>401</v>
+        <v>414</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9658,7 +9731,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9670,17 +9743,17 @@
         <v>34</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c t="s" r="K236" s="7">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>403</v>
+        <v>416</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9695,7 +9768,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9707,7 +9780,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>180</v>
@@ -9743,7 +9816,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9752,7 +9825,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="I239" s="7">
         <v>203</v>
@@ -9763,7 +9836,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>406</v>
+        <v>419</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9778,13 +9851,13 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="H240" s="8">
         <v>57</v>
@@ -9793,12 +9866,12 @@
         <v>23</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>408</v>
+        <v>421</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9813,7 +9886,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9825,15 +9898,15 @@
         <v>195</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>409</v>
+        <v>422</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9848,7 +9921,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9863,11 +9936,13 @@
         <v>240</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
-      <c r="M242" s="7"/>
+      <c t="s" r="M242" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
       <c r="A243" s="6"/>
@@ -9896,7 +9971,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9931,7 +10006,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9943,15 +10018,15 @@
         <v>44</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>412</v>
+        <v>426</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9966,7 +10041,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9981,14 +10056,14 @@
         <v>108</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c t="s" r="K246" s="7">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>415</v>
+        <v>429</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -10003,7 +10078,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -10018,14 +10093,14 @@
         <v>70</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c t="s" r="K247" s="7">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>416</v>
+        <v>430</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -10040,7 +10115,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -10060,7 +10135,7 @@
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>417</v>
+        <v>431</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -10075,7 +10150,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -10084,10 +10159,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>213</v>
@@ -10095,7 +10170,7 @@
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>418</v>
+        <v>432</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -10110,29 +10185,29 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>95</v>
       </c>
       <c t="s" r="K250" s="7">
-        <v>214</v>
+        <v>300</v>
       </c>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>289</v>
+        <v>433</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -10162,7 +10237,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -10182,7 +10257,7 @@
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>420</v>
+        <v>435</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -10197,7 +10272,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -10209,15 +10284,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>422</v>
+        <v>437</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -10232,7 +10307,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -10241,18 +10316,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>423</v>
+        <v>438</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10267,13 +10342,13 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>34</v>
@@ -10287,7 +10362,7 @@
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -10317,7 +10392,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -10337,7 +10412,7 @@
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10352,7 +10427,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10364,7 +10439,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>108</v>
@@ -10372,7 +10447,7 @@
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>426</v>
+        <v>441</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10387,7 +10462,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -10399,15 +10474,15 @@
         <v>72</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>428</v>
+        <v>443</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10422,7 +10497,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10442,7 +10517,7 @@
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10457,7 +10532,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10466,18 +10541,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>91</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>429</v>
+        <v>444</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -10492,13 +10567,13 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>34</v>
@@ -10507,11 +10582,13 @@
         <v>25</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>214</v>
+        <v>300</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
-      <c r="M262" s="7"/>
+      <c t="s" r="M262" s="7">
+        <v>339</v>
+      </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
       <c r="A263" s="6"/>
@@ -10540,7 +10617,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -10549,18 +10626,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>433</v>
+        <v>448</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10575,13 +10652,13 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>34</v>
@@ -10595,7 +10672,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>434</v>
+        <v>449</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10610,7 +10687,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
@@ -10622,15 +10699,15 @@
         <v>154</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>435</v>
+        <v>450</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10645,7 +10722,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
@@ -10665,7 +10742,7 @@
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10680,7 +10757,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -10702,7 +10779,7 @@
       </c>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>436</v>
+        <v>451</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10717,7 +10794,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -10729,13 +10806,13 @@
         <v>34</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>199</v>
       </c>
       <c t="s" r="K269" s="7">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
@@ -10769,7 +10846,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10781,15 +10858,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>439</v>
+        <v>454</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10804,7 +10881,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10824,7 +10901,7 @@
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>440</v>
+        <v>455</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10839,7 +10916,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10859,7 +10936,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>441</v>
+        <v>456</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10874,7 +10951,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10883,10 +10960,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>45</v>
@@ -10894,7 +10971,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>443</v>
+        <v>458</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10909,19 +10986,19 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>51</v>
@@ -10961,7 +11038,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10970,7 +11047,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c t="s" r="I277" s="7">
         <v>81</v>
@@ -10981,7 +11058,7 @@
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>447</v>
+        <v>462</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -10996,22 +11073,22 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -11031,7 +11108,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -11040,7 +11117,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c t="s" r="I279" s="7">
         <v>208</v>
@@ -11066,27 +11143,27 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>214</v>
+        <v>300</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>450</v>
+        <v>465</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -11101,7 +11178,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -11149,7 +11226,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -11158,18 +11235,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>454</v>
+        <v>469</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -11184,13 +11261,13 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>57</v>
@@ -11204,7 +11281,7 @@
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -11219,7 +11296,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -11228,7 +11305,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I285" s="7">
         <v>23</v>
@@ -11239,7 +11316,7 @@
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>455</v>
+        <v>470</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -11254,27 +11331,27 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>456</v>
+        <v>471</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11304,7 +11381,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -11313,7 +11390,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I288" s="7">
         <v>151</v>
@@ -11324,7 +11401,7 @@
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -11339,16 +11416,16 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c t="s" r="I289" s="7">
         <v>35</v>
@@ -11359,7 +11436,7 @@
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>458</v>
+        <v>473</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -11374,27 +11451,27 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I290" s="7">
         <v>85</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11409,13 +11486,13 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>34</v>
@@ -11424,12 +11501,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>459</v>
+        <v>474</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11444,7 +11521,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -11456,7 +11533,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>116</v>
@@ -11464,7 +11541,7 @@
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>460</v>
+        <v>475</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11479,7 +11556,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -11499,7 +11576,7 @@
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>461</v>
+        <v>476</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11514,7 +11591,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -11523,10 +11600,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>69</v>
@@ -11562,7 +11639,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -11571,18 +11648,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>466</v>
+        <v>481</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11597,19 +11674,19 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>203</v>
@@ -11617,7 +11694,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>468</v>
+        <v>483</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11632,27 +11709,27 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>469</v>
+        <v>484</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11667,13 +11744,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>57</v>
@@ -11702,7 +11779,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11714,10 +11791,10 @@
         <v>195</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -11737,7 +11814,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11752,12 +11829,12 @@
         <v>113</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>339</v>
+        <v>348</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11772,7 +11849,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11784,7 +11861,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>201</v>
@@ -11792,7 +11869,7 @@
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>471</v>
+        <v>486</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11822,7 +11899,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -11842,7 +11919,7 @@
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>473</v>
+        <v>488</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11857,7 +11934,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -11877,7 +11954,7 @@
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>474</v>
+        <v>489</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11892,7 +11969,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11912,7 +11989,7 @@
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>475</v>
+        <v>490</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11927,7 +12004,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11939,7 +12016,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>212</v>
@@ -11962,7 +12039,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11997,7 +12074,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -12009,14 +12086,16 @@
         <v>57</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>175</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
-      <c r="M309" s="7"/>
+      <c t="s" r="M309" s="7">
+        <v>491</v>
+      </c>
     </row>
     <row r="310" ht="15" customHeight="1">
       <c r="A310" s="6"/>
@@ -12038,14 +12117,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B311" s="7">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c t="s" r="C311" s="7">
         <v>14</v>
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -12067,7 +12146,7 @@
       </c>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>478</v>
+        <v>494</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -12075,14 +12154,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B312" s="7">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c t="s" r="C312" s="7">
         <v>14</v>
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -12097,12 +12176,12 @@
         <v>108</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>480</v>
+        <v>496</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -12117,7 +12196,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -12129,7 +12208,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>225</v>
@@ -12139,7 +12218,7 @@
       </c>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>481</v>
+        <v>497</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -12154,7 +12233,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -12204,7 +12283,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -12213,18 +12292,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>484</v>
+        <v>500</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -12239,13 +12318,13 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>57</v>
@@ -12254,14 +12333,14 @@
         <v>21</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="K317" s="7">
         <v>61</v>
       </c>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>485</v>
+        <v>501</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -12276,7 +12355,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -12296,7 +12375,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>486</v>
+        <v>502</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12311,7 +12390,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -12323,15 +12402,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>487</v>
+        <v>503</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12346,7 +12425,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -12361,14 +12440,14 @@
         <v>213</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c t="s" r="K320" s="7">
-        <v>214</v>
+        <v>300</v>
       </c>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>217</v>
+        <v>273</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12398,7 +12477,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -12407,7 +12486,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>205</v>
@@ -12433,19 +12512,19 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>74</v>
@@ -12453,7 +12532,7 @@
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>490</v>
+        <v>506</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12468,7 +12547,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -12503,7 +12582,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12515,17 +12594,17 @@
         <v>34</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c t="s" r="K325" s="7">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>492</v>
+        <v>508</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12555,7 +12634,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12564,18 +12643,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>189</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>494</v>
+        <v>510</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -12590,27 +12669,27 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>495</v>
+        <v>511</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>496</v>
+        <v>512</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12625,7 +12704,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -12645,7 +12724,7 @@
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>497</v>
+        <v>513</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12660,7 +12739,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -12672,17 +12751,17 @@
         <v>57</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>206</v>
       </c>
       <c t="s" r="K330" s="7">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>499</v>
+        <v>515</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12697,7 +12776,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -12706,16 +12785,16 @@
         <v>57</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c t="s" r="I331" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c t="s" r="K331" s="7">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
@@ -12734,13 +12813,13 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>57</v>
@@ -12756,7 +12835,7 @@
       </c>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>501</v>
+        <v>517</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12771,7 +12850,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12780,7 +12859,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c t="s" r="I333" s="7">
         <v>172</v>
@@ -12791,7 +12870,7 @@
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12806,27 +12885,27 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>450</v>
+        <v>465</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12856,7 +12935,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -12865,10 +12944,10 @@
         <v>44</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>73</v>
@@ -12891,13 +12970,13 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>44</v>
@@ -12906,7 +12985,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -12926,7 +13005,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12935,10 +13014,10 @@
         <v>44</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>51</v>
@@ -12946,7 +13025,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>504</v>
+        <v>520</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12961,26 +13040,28 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
-      <c r="M339" s="7"/>
+      <c t="s" r="M339" s="7">
+        <v>521</v>
+      </c>
     </row>
     <row r="340" ht="15" customHeight="1">
       <c r="A340" s="6"/>
@@ -13009,7 +13090,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -13024,12 +13105,12 @@
         <v>180</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>506</v>
+        <v>523</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -13044,7 +13125,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -13053,18 +13134,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c t="s" r="I342" s="7">
+        <v>345</v>
+      </c>
+      <c t="s" r="J342" s="7">
         <v>336</v>
-      </c>
-      <c t="s" r="J342" s="7">
-        <v>328</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>507</v>
+        <v>524</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -13079,13 +13160,13 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>57</v>
@@ -13094,12 +13175,12 @@
         <v>41</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>508</v>
+        <v>525</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -13114,7 +13195,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -13123,7 +13204,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>509</v>
+        <v>526</v>
       </c>
       <c t="s" r="I344" s="7">
         <v>45</v>
@@ -13132,11 +13213,11 @@
         <v>133</v>
       </c>
       <c t="s" r="K344" s="7">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>510</v>
+        <v>527</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -13151,22 +13232,22 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>509</v>
+        <v>526</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>511</v>
+        <v>528</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -13199,7 +13280,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -13208,18 +13289,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>513</v>
+        <v>530</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -13234,19 +13315,19 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>205</v>
@@ -13254,7 +13335,7 @@
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>514</v>
+        <v>531</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -13269,7 +13350,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -13281,7 +13362,7 @@
         <v>195</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c t="s" r="J349" s="7">
         <v>21</v>
@@ -13304,7 +13385,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -13316,7 +13397,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>228</v>
@@ -13324,7 +13405,7 @@
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>515</v>
+        <v>532</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13339,7 +13420,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -13348,18 +13429,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>516</v>
+        <v>533</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13374,13 +13455,13 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>57</v>
@@ -13389,12 +13470,12 @@
         <v>49</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>517</v>
+        <v>534</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -13424,7 +13505,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -13436,10 +13517,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="K354" s="7">
         <v>181</v>
@@ -13461,7 +13542,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -13481,7 +13562,7 @@
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>519</v>
+        <v>536</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -13496,7 +13577,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -13516,7 +13597,7 @@
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>520</v>
+        <v>537</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -13531,7 +13612,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13540,10 +13621,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>122</v>
@@ -13551,7 +13632,7 @@
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>522</v>
+        <v>539</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13566,22 +13647,22 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>523</v>
+        <v>540</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>524</v>
+        <v>541</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -13614,7 +13695,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13626,7 +13707,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>59</v>
@@ -13634,7 +13715,7 @@
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>526</v>
+        <v>543</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13649,7 +13730,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13664,12 +13745,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>527</v>
+        <v>544</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13684,7 +13765,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13699,12 +13780,12 @@
         <v>70</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>528</v>
+        <v>545</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13719,7 +13800,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13731,7 +13812,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>77</v>
@@ -13754,7 +13835,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13766,7 +13847,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c t="s" r="J364" s="7">
         <v>103</v>
@@ -13774,7 +13855,7 @@
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13789,7 +13870,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13804,11 +13885,13 @@
         <v>240</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>52</v>
+        <v>370</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
-      <c r="M365" s="7"/>
+      <c t="s" r="M365" s="7">
+        <v>175</v>
+      </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
       <c t="s" r="A366" s="6">
@@ -13822,7 +13905,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -13870,7 +13953,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13879,18 +13962,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c t="s" r="I368" s="7">
         <v>84</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>530</v>
+        <v>547</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13905,19 +13988,19 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>61</v>
@@ -13925,7 +14008,7 @@
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>531</v>
+        <v>548</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13940,7 +14023,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -13949,10 +14032,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c t="s" r="J370" s="7">
         <v>91</v>
@@ -13960,7 +14043,7 @@
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>532</v>
+        <v>549</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13975,13 +14058,13 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>34</v>
@@ -13990,12 +14073,12 @@
         <v>128</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>533</v>
+        <v>550</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -14010,7 +14093,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -14019,17 +14102,19 @@
         <v>34</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>534</v>
+        <v>266</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
-      <c r="M372" s="7"/>
+      <c t="s" r="M372" s="7">
+        <v>551</v>
+      </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
       <c t="s" r="A373" s="6">
@@ -14043,22 +14128,22 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -14091,7 +14176,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -14103,15 +14188,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>538</v>
+        <v>555</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>539</v>
+        <v>556</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -14141,7 +14226,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -14176,7 +14261,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -14196,7 +14281,7 @@
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -14211,7 +14296,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -14223,7 +14308,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>41</v>
@@ -14231,7 +14316,7 @@
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>541</v>
+        <v>558</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -14246,7 +14331,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -14258,10 +14343,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -14281,7 +14366,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -14293,7 +14378,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>26</v>
@@ -14301,7 +14386,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>542</v>
+        <v>559</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -14316,7 +14401,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -14331,14 +14416,14 @@
         <v>51</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="K382" s="7">
-        <v>214</v>
+        <v>300</v>
       </c>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>217</v>
+        <v>560</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -14353,7 +14438,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -14365,7 +14450,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>511</v>
+        <v>528</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>137</v>
@@ -14401,7 +14486,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14413,7 +14498,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>137</v>
@@ -14421,7 +14506,7 @@
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>544</v>
+        <v>562</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -14436,7 +14521,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -14451,12 +14536,12 @@
         <v>192</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>411</v>
+        <v>425</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14471,7 +14556,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -14483,7 +14568,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>198</v>
@@ -14491,7 +14576,7 @@
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>545</v>
+        <v>563</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -14506,7 +14591,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -14515,18 +14600,18 @@
         <v>107</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I388" s="7">
         <v>102</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>546</v>
+        <v>564</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14541,19 +14626,19 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>107</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>213</v>
@@ -14578,7 +14663,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -14590,10 +14675,10 @@
         <v>76</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -14626,7 +14711,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -14646,7 +14731,7 @@
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>550</v>
+        <v>568</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14661,7 +14746,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -14681,7 +14766,7 @@
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>551</v>
+        <v>569</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14696,7 +14781,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14731,7 +14816,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14746,12 +14831,12 @@
         <v>143</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>552</v>
+        <v>214</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14766,7 +14851,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14775,10 +14860,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>176</v>
@@ -14799,22 +14884,22 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c t="s" r="H397" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -14847,7 +14932,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -14856,7 +14941,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c t="s" r="I399" s="7">
         <v>98</v>
@@ -14867,7 +14952,7 @@
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>557</v>
+        <v>574</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -14882,13 +14967,13 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>57</v>
@@ -14897,7 +14982,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -14917,7 +15002,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14932,12 +15017,12 @@
         <v>84</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>558</v>
+        <v>575</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14952,7 +15037,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14964,15 +15049,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>560</v>
+        <v>577</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14987,7 +15072,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -15002,12 +15087,12 @@
         <v>23</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>561</v>
+        <v>578</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -15022,7 +15107,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -15034,7 +15119,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>164</v>
@@ -15042,7 +15127,7 @@
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>423</v>
+        <v>438</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -15057,7 +15142,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -15069,15 +15154,15 @@
         <v>191</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>562</v>
+        <v>579</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -15092,7 +15177,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -15112,7 +15197,7 @@
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>563</v>
+        <v>580</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -15127,7 +15212,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -15139,10 +15224,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>510</v>
+        <v>527</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -15160,7 +15245,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -15169,10 +15254,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>100</v>
@@ -15208,7 +15293,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -15217,18 +15302,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c t="s" r="I410" s="7">
         <v>67</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>506</v>
+        <v>523</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>433</v>
+        <v>448</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -15243,27 +15328,27 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>538</v>
+        <v>555</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>566</v>
+        <v>583</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -15278,7 +15363,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -15287,18 +15372,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I412" s="7">
         <v>223</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>567</v>
+        <v>584</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15313,19 +15398,19 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>61</v>
@@ -15333,7 +15418,7 @@
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>568</v>
+        <v>585</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15348,7 +15433,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -15360,17 +15445,17 @@
         <v>57</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c t="s" r="K414" s="7">
         <v>198</v>
       </c>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>569</v>
+        <v>586</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -15385,7 +15470,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -15403,11 +15488,11 @@
         <v>46</v>
       </c>
       <c t="s" r="K415" s="7">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>570</v>
+        <v>587</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -15422,7 +15507,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -15444,7 +15529,7 @@
       </c>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>175</v>
+        <v>588</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -15474,7 +15559,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="F418" s="7">
         <v>320</v>
@@ -15494,7 +15579,7 @@
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>572</v>
+        <v>590</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -15509,7 +15594,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="F419" s="7">
         <v>320</v>
@@ -15521,7 +15606,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>38</v>
@@ -15529,7 +15614,7 @@
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>573</v>
+        <v>591</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -15544,7 +15629,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="F420" s="7">
         <v>320</v>
@@ -15553,10 +15638,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J420" s="7">
         <v>74</v>
@@ -15564,7 +15649,7 @@
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>403</v>
+        <v>416</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -15579,29 +15664,29 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="H421" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c t="s" r="K421" s="7">
         <v>164</v>
       </c>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>574</v>
+        <v>592</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -15616,7 +15701,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -15625,18 +15710,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>509</v>
+        <v>526</v>
       </c>
       <c t="s" r="I422" s="7">
         <v>49</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>575</v>
+        <v>275</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -15651,22 +15736,22 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>509</v>
+        <v>526</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>577</v>
+        <v>594</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -15699,7 +15784,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -15711,15 +15796,15 @@
         <v>72</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>432</v>
+        <v>447</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -15734,7 +15819,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -15754,7 +15839,7 @@
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>580</v>
+        <v>597</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15769,7 +15854,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -15781,15 +15866,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
-        <v>581</v>
+        <v>598</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -15804,7 +15889,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -15816,7 +15901,7 @@
         <v>114</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c t="s" r="J428" s="7">
         <v>115</v>
@@ -15824,7 +15909,7 @@
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>582</v>
+        <v>599</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -15839,7 +15924,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -15854,12 +15939,12 @@
         <v>164</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
       <c t="s" r="M429" s="7">
-        <v>583</v>
+        <v>600</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
@@ -15874,7 +15959,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -15889,12 +15974,12 @@
         <v>46</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>584</v>
+        <v>601</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -15909,7 +15994,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F431" s="7">
         <v>321</v>
@@ -15957,7 +16042,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -15969,7 +16054,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>506</v>
+        <v>523</v>
       </c>
       <c t="s" r="J433" s="7">
         <v>126</v>
@@ -15977,7 +16062,7 @@
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>580</v>
+        <v>597</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -15992,7 +16077,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -16004,10 +16089,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -16027,7 +16112,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -16039,7 +16124,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="J435" s="7">
         <v>103</v>
@@ -16049,7 +16134,7 @@
       </c>
       <c r="L435" s="7"/>
       <c t="s" r="M435" s="7">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="436" ht="14.25" customHeight="1">
@@ -16064,7 +16149,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -16079,14 +16164,14 @@
         <v>144</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c t="s" r="K436" s="7">
         <v>216</v>
       </c>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>547</v>
+        <v>603</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -16101,7 +16186,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -16113,10 +16198,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -16149,7 +16234,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -16164,12 +16249,12 @@
         <v>233</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>587</v>
+        <v>605</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -16184,7 +16269,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -16196,7 +16281,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>495</v>
+        <v>511</v>
       </c>
       <c t="s" r="J440" s="7">
         <v>69</v>
@@ -16204,7 +16289,7 @@
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>588</v>
+        <v>606</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -16219,7 +16304,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -16231,15 +16316,15 @@
         <v>44</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>589</v>
+        <v>607</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
       <c t="s" r="M441" s="7">
-        <v>590</v>
+        <v>608</v>
       </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
@@ -16254,7 +16339,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -16269,7 +16354,7 @@
         <v>140</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -16289,7 +16374,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -16309,7 +16394,7 @@
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>591</v>
+        <v>609</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -16339,7 +16424,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="F445" s="7">
         <v>320</v>
@@ -16348,10 +16433,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H445" s="8">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>593</v>
+        <v>611</v>
       </c>
       <c t="s" r="J445" s="7">
         <v>233</v>
@@ -16359,7 +16444,7 @@
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
       <c t="s" r="M445" s="7">
-        <v>594</v>
+        <v>612</v>
       </c>
     </row>
     <row r="446" ht="14.25" customHeight="1">
@@ -16374,13 +16459,13 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G446" s="8">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c t="s" r="H446" s="8">
         <v>57</v>
@@ -16394,7 +16479,7 @@
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>595</v>
+        <v>613</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -16409,7 +16494,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="F447" s="7">
         <v>320</v>
@@ -16418,18 +16503,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H447" s="8">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c t="s" r="I447" s="7">
         <v>35</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>596</v>
+        <v>614</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -16444,13 +16529,13 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G448" s="8">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c t="s" r="H448" s="8">
         <v>57</v>
@@ -16459,12 +16544,12 @@
         <v>205</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
-        <v>597</v>
+        <v>615</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -16479,7 +16564,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
@@ -16491,7 +16576,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c t="s" r="J449" s="7">
         <v>39</v>
@@ -16499,7 +16584,7 @@
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
-        <v>507</v>
+        <v>524</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1">
@@ -16514,7 +16599,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
@@ -16523,7 +16608,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H450" s="8">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c t="s" r="I450" s="7">
         <v>41</v>
@@ -16532,11 +16617,11 @@
         <v>77</v>
       </c>
       <c t="s" r="K450" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="L450" s="7"/>
       <c t="s" r="M450" s="7">
-        <v>598</v>
+        <v>616</v>
       </c>
     </row>
     <row r="451" ht="14.25" customHeight="1">
@@ -16551,29 +16636,29 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G451" s="8">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c t="s" r="H451" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c t="s" r="K451" s="7">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="L451" s="7"/>
       <c t="s" r="M451" s="7">
-        <v>599</v>
+        <v>617</v>
       </c>
     </row>
     <row r="452" ht="14.25" customHeight="1">
@@ -16603,7 +16688,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>600</v>
+        <v>618</v>
       </c>
       <c r="F453" s="7">
         <v>330</v>
@@ -16615,15 +16700,15 @@
         <v>44</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c t="s" r="M453" s="7">
-        <v>601</v>
+        <v>619</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -16638,7 +16723,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>600</v>
+        <v>618</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
@@ -16647,18 +16732,18 @@
         <v>44</v>
       </c>
       <c t="s" r="H454" s="8">
-        <v>602</v>
+        <v>620</v>
       </c>
       <c t="s" r="I454" s="7">
         <v>35</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
       <c t="s" r="M454" s="7">
-        <v>344</v>
+        <v>353</v>
       </c>
     </row>
     <row r="455" ht="15" customHeight="1">
@@ -16673,13 +16758,13 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>600</v>
+        <v>618</v>
       </c>
       <c r="F455" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G455" s="8">
-        <v>602</v>
+        <v>620</v>
       </c>
       <c t="s" r="H455" s="8">
         <v>44</v>
@@ -16688,12 +16773,12 @@
         <v>42</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>603</v>
+        <v>621</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -16723,7 +16808,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>604</v>
+        <v>622</v>
       </c>
       <c r="F457" s="7">
         <v>330</v>
@@ -16735,15 +16820,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
       <c t="s" r="M457" s="7">
-        <v>605</v>
+        <v>623</v>
       </c>
     </row>
     <row r="458" ht="14.25" customHeight="1">
@@ -16773,13 +16858,13 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>606</v>
+        <v>624</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G459" s="8">
-        <v>607</v>
+        <v>625</v>
       </c>
       <c t="s" r="H459" s="8">
         <v>57</v>
@@ -16788,12 +16873,12 @@
         <v>138</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
       <c t="s" r="M459" s="7">
-        <v>515</v>
+        <v>532</v>
       </c>
     </row>
     <row r="460" ht="15" customHeight="1">
@@ -16808,7 +16893,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>606</v>
+        <v>624</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
@@ -16817,17 +16902,19 @@
         <v>57</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>607</v>
+        <v>625</v>
       </c>
       <c t="s" r="I460" s="7">
         <v>49</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
-      <c r="M460" s="7"/>
+      <c t="s" r="M460" s="7">
+        <v>626</v>
+      </c>
     </row>
     <row r="461" ht="14.25" customHeight="1">
       <c r="A461" s="6"/>
@@ -16856,7 +16943,7 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="F462" s="7">
         <v>330</v>
@@ -16871,12 +16958,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J462" s="7">
-        <v>589</v>
+        <v>607</v>
       </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
       <c t="s" r="M462" s="7">
-        <v>609</v>
+        <v>628</v>
       </c>
     </row>
     <row r="463" ht="14.25" customHeight="1">
@@ -16891,7 +16978,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
@@ -16900,7 +16987,7 @@
         <v>44</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>610</v>
+        <v>629</v>
       </c>
       <c t="s" r="I463" s="7">
         <v>156</v>
@@ -16911,7 +16998,7 @@
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
       <c t="s" r="M463" s="7">
-        <v>611</v>
+        <v>630</v>
       </c>
     </row>
     <row r="464" ht="14.25" customHeight="1">
@@ -16926,13 +17013,13 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>610</v>
+        <v>629</v>
       </c>
       <c t="s" r="H464" s="8">
         <v>44</v>
@@ -16974,13 +17061,13 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>612</v>
+        <v>631</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G466" s="8">
-        <v>613</v>
+        <v>632</v>
       </c>
       <c t="s" r="H466" s="8">
         <v>17</v>
@@ -16989,12 +17076,12 @@
         <v>151</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
       <c t="s" r="M466" s="7">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="467" ht="14.25" customHeight="1">
@@ -17024,7 +17111,7 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>614</v>
+        <v>633</v>
       </c>
       <c r="F468" s="7">
         <v>330</v>
@@ -17044,7 +17131,7 @@
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
       <c t="s" r="M468" s="7">
-        <v>435</v>
+        <v>450</v>
       </c>
     </row>
     <row r="469" ht="14.25" customHeight="1">
@@ -17074,7 +17161,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>615</v>
+        <v>634</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
@@ -17083,18 +17170,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>616</v>
+        <v>635</v>
       </c>
       <c t="s" r="I470" s="7">
         <v>138</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>214</v>
+        <v>300</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
       <c t="s" r="M470" s="7">
-        <v>617</v>
+        <v>636</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
@@ -17109,13 +17196,13 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>615</v>
+        <v>634</v>
       </c>
       <c r="F471" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G471" s="8">
-        <v>616</v>
+        <v>635</v>
       </c>
       <c t="s" r="H471" s="8">
         <v>57</v>
@@ -17124,15 +17211,17 @@
         <v>27</v>
       </c>
       <c t="s" r="J471" s="7">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
-      <c r="M471" s="7"/>
+      <c t="s" r="M471" s="7">
+        <v>219</v>
+      </c>
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c t="s" r="A472" s="9">
-        <v>618</v>
+        <v>637</v>
       </c>
       <c r="B472" s="9"/>
       <c r="C472" s="9"/>
@@ -17152,7 +17241,7 @@
     <row r="473" ht="65.25" customHeight="1"/>
     <row r="474" ht="16.5" customHeight="1">
       <c t="s" r="A474" s="10">
-        <v>619</v>
+        <v>638</v>
       </c>
       <c r="B474" s="10"/>
       <c r="C474" s="10"/>
@@ -17165,7 +17254,7 @@
       <c r="J474" s="10"/>
       <c r="K474" s="10"/>
       <c t="s" r="L474" s="11">
-        <v>620</v>
+        <v>639</v>
       </c>
       <c r="M474" s="11"/>
       <c r="N474" s="11"/>
